--- a/132_Cuenca_Quilca_-_Vitor_-_Chili/_raw_reportes_xlsx/IDConfig_64128_completo.xlsx
+++ b/132_Cuenca_Quilca_-_Vitor_-_Chili/_raw_reportes_xlsx/IDConfig_64128_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Recf3fd27437142ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rd4b1d82e69e147f4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 382413.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 364562.1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 346860.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 345422.4000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 337514.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 321326.7000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 304156.4000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 284254.7000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 264960.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/132_Cuenca_Quilca_-_Vitor_-_Chili/_raw_reportes_xlsx/IDConfig_64128_completo.xlsx
+++ b/132_Cuenca_Quilca_-_Vitor_-_Chili/_raw_reportes_xlsx/IDConfig_64128_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rd4b1d82e69e147f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R5b41254b85f04927"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 193238.9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 173477.4000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 153376.2000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 134434.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 113602.6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>  94086.6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>  74643.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>  54542.6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>  34679.8000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>  19312.4000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 571454.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 553435.5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 533854.4000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 514421.8000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 495863.5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 475916.5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 457297.8000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 437449.1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 418474.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 398571.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 378964.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 358909.5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 339116.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 321143.5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 302997.5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 284449.6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 266922.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 247648.1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 229612.1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 210061.8000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 190412.1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 171916.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 152461.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 133766.6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 114868.9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>  96666.1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>  77198.6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>  57887.7000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>  38250.1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>  19204.9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 540697.6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 520737.6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 501468.2000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 480755.1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 461182.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 442006.4000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 420958.4000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v> 401913.6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
